--- a/Pruebas calificadas/COLEGIO ROGELIO SALMONA (IED) 703_CALIFICADO.xlsx
+++ b/Pruebas calificadas/COLEGIO ROGELIO SALMONA (IED) 703_CALIFICADO.xlsx
@@ -1617,9 +1617,9 @@
           <t>D</t>
         </is>
       </c>
-      <c r="L5" s="3" t="inlineStr">
-        <is>
-          <t>INCORRECTO</t>
+      <c r="L5" s="4" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
@@ -2123,9 +2123,9 @@
           <t>B</t>
         </is>
       </c>
-      <c r="L7" s="4" t="inlineStr">
-        <is>
-          <t>CORRECTO</t>
+      <c r="L7" s="3" t="inlineStr">
+        <is>
+          <t>INCORRECTO</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
@@ -3633,9 +3633,9 @@
           <t>D</t>
         </is>
       </c>
-      <c r="L13" s="3" t="inlineStr">
-        <is>
-          <t>INCORRECTO</t>
+      <c r="L13" s="4" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
@@ -4139,9 +4139,9 @@
           <t>D</t>
         </is>
       </c>
-      <c r="L15" s="3" t="inlineStr">
-        <is>
-          <t>INCORRECTO</t>
+      <c r="L15" s="4" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
@@ -6629,9 +6629,9 @@
           <t>B</t>
         </is>
       </c>
-      <c r="L25" s="4" t="inlineStr">
-        <is>
-          <t>CORRECTO</t>
+      <c r="L25" s="3" t="inlineStr">
+        <is>
+          <t>INCORRECTO</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
@@ -7135,9 +7135,9 @@
           <t>B</t>
         </is>
       </c>
-      <c r="L27" s="4" t="inlineStr">
-        <is>
-          <t>CORRECTO</t>
+      <c r="L27" s="3" t="inlineStr">
+        <is>
+          <t>INCORRECTO</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
@@ -7641,9 +7641,9 @@
           <t>D</t>
         </is>
       </c>
-      <c r="L29" s="3" t="inlineStr">
-        <is>
-          <t>INCORRECTO</t>
+      <c r="L29" s="4" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
@@ -9155,9 +9155,9 @@
           <t>D</t>
         </is>
       </c>
-      <c r="L35" s="3" t="inlineStr">
-        <is>
-          <t>INCORRECTO</t>
+      <c r="L35" s="4" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
@@ -9661,9 +9661,9 @@
           <t>D</t>
         </is>
       </c>
-      <c r="L37" s="3" t="inlineStr">
-        <is>
-          <t>INCORRECTO</t>
+      <c r="L37" s="4" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
@@ -10167,9 +10167,9 @@
           <t>D</t>
         </is>
       </c>
-      <c r="L39" s="3" t="inlineStr">
-        <is>
-          <t>INCORRECTO</t>
+      <c r="L39" s="4" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
         </is>
       </c>
       <c r="M39" s="2" t="inlineStr">
@@ -10673,9 +10673,9 @@
           <t>B</t>
         </is>
       </c>
-      <c r="L41" s="4" t="inlineStr">
-        <is>
-          <t>CORRECTO</t>
+      <c r="L41" s="3" t="inlineStr">
+        <is>
+          <t>INCORRECTO</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
@@ -11099,9 +11099,9 @@
           <t>D</t>
         </is>
       </c>
-      <c r="L43" s="3" t="inlineStr">
-        <is>
-          <t>INCORRECTO</t>
+      <c r="L43" s="4" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
         </is>
       </c>
       <c r="M43" s="2" t="inlineStr">
@@ -11601,9 +11601,9 @@
           <t>B</t>
         </is>
       </c>
-      <c r="L45" s="4" t="inlineStr">
-        <is>
-          <t>CORRECTO</t>
+      <c r="L45" s="3" t="inlineStr">
+        <is>
+          <t>INCORRECTO</t>
         </is>
       </c>
       <c r="M45" s="2" t="inlineStr">
@@ -12107,9 +12107,9 @@
           <t>B</t>
         </is>
       </c>
-      <c r="L47" s="4" t="inlineStr">
-        <is>
-          <t>CORRECTO</t>
+      <c r="L47" s="3" t="inlineStr">
+        <is>
+          <t>INCORRECTO</t>
         </is>
       </c>
       <c r="M47" s="2" t="inlineStr">
@@ -12613,9 +12613,9 @@
           <t>D</t>
         </is>
       </c>
-      <c r="L49" s="3" t="inlineStr">
-        <is>
-          <t>INCORRECTO</t>
+      <c r="L49" s="4" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
         </is>
       </c>
       <c r="M49" s="2" t="inlineStr">
@@ -13119,9 +13119,9 @@
           <t>D</t>
         </is>
       </c>
-      <c r="L51" s="3" t="inlineStr">
-        <is>
-          <t>INCORRECTO</t>
+      <c r="L51" s="4" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
         </is>
       </c>
       <c r="M51" s="2" t="inlineStr">
@@ -14127,9 +14127,9 @@
           <t>D</t>
         </is>
       </c>
-      <c r="L55" s="3" t="inlineStr">
-        <is>
-          <t>INCORRECTO</t>
+      <c r="L55" s="4" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
         </is>
       </c>
       <c r="M55" s="2" t="inlineStr">
@@ -15605,9 +15605,9 @@
           <t>D</t>
         </is>
       </c>
-      <c r="L61" s="3" t="inlineStr">
-        <is>
-          <t>INCORRECTO</t>
+      <c r="L61" s="4" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
         </is>
       </c>
       <c r="M61" s="2" t="inlineStr">
@@ -17123,9 +17123,9 @@
           <t>B</t>
         </is>
       </c>
-      <c r="L67" s="4" t="inlineStr">
-        <is>
-          <t>CORRECTO</t>
+      <c r="L67" s="3" t="inlineStr">
+        <is>
+          <t>INCORRECTO</t>
         </is>
       </c>
       <c r="M67" s="2" t="inlineStr">
@@ -17629,9 +17629,9 @@
           <t>D</t>
         </is>
       </c>
-      <c r="L69" s="3" t="inlineStr">
-        <is>
-          <t>INCORRECTO</t>
+      <c r="L69" s="4" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
         </is>
       </c>
       <c r="M69" s="2" t="inlineStr">
@@ -18135,9 +18135,9 @@
           <t>D</t>
         </is>
       </c>
-      <c r="L71" s="3" t="inlineStr">
-        <is>
-          <t>INCORRECTO</t>
+      <c r="L71" s="4" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
         </is>
       </c>
       <c r="M71" s="2" t="inlineStr">
@@ -21159,9 +21159,9 @@
           <t>D</t>
         </is>
       </c>
-      <c r="L83" s="3" t="inlineStr">
-        <is>
-          <t>INCORRECTO</t>
+      <c r="L83" s="4" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
         </is>
       </c>
       <c r="M83" s="2" t="inlineStr">
@@ -21665,9 +21665,9 @@
           <t>D</t>
         </is>
       </c>
-      <c r="L85" s="3" t="inlineStr">
-        <is>
-          <t>INCORRECTO</t>
+      <c r="L85" s="4" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
         </is>
       </c>
       <c r="M85" s="2" t="inlineStr">

--- a/Pruebas calificadas/COLEGIO ROGELIO SALMONA (IED) 703_CALIFICADO.xlsx
+++ b/Pruebas calificadas/COLEGIO ROGELIO SALMONA (IED) 703_CALIFICADO.xlsx
@@ -807,11 +807,7 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A2" s="2" t="inlineStr"/>
       <c r="B2" s="2" t="inlineStr">
         <is>
           <t>111001800422</t>
@@ -819,7 +815,7 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO ROGELIO SALMONA (IED)</t>
+          <t>COLEGIO ROGELIO SALMONA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
@@ -1060,11 +1056,7 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A3" s="2" t="inlineStr"/>
       <c r="B3" s="2" t="inlineStr">
         <is>
           <t>111001800422</t>
@@ -1072,7 +1064,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO ROGELIO SALMONA (IED)</t>
+          <t>COLEGIO ROGELIO SALMONA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
@@ -1313,11 +1305,7 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A4" s="2" t="inlineStr"/>
       <c r="B4" s="2" t="inlineStr">
         <is>
           <t>111001800422</t>
@@ -1325,7 +1313,7 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO ROGELIO SALMONA (IED)</t>
+          <t>COLEGIO ROGELIO SALMONA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
@@ -1566,11 +1554,7 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A5" s="2" t="inlineStr"/>
       <c r="B5" s="2" t="inlineStr">
         <is>
           <t>111001800422</t>
@@ -1578,7 +1562,7 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO ROGELIO SALMONA (IED)</t>
+          <t>COLEGIO ROGELIO SALMONA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
@@ -1819,11 +1803,7 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A6" s="2" t="inlineStr"/>
       <c r="B6" s="2" t="inlineStr">
         <is>
           <t>111001800422</t>
@@ -1831,7 +1811,7 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO ROGELIO SALMONA (IED)</t>
+          <t>COLEGIO ROGELIO SALMONA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
@@ -2072,11 +2052,7 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A7" s="2" t="inlineStr"/>
       <c r="B7" s="2" t="inlineStr">
         <is>
           <t>111001800422</t>
@@ -2084,7 +2060,7 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO ROGELIO SALMONA (IED)</t>
+          <t>COLEGIO ROGELIO SALMONA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
@@ -2325,11 +2301,7 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A8" s="2" t="inlineStr"/>
       <c r="B8" s="2" t="inlineStr">
         <is>
           <t>111001800422</t>
@@ -2337,7 +2309,7 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO ROGELIO SALMONA (IED)</t>
+          <t>COLEGIO ROGELIO SALMONA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
@@ -2578,11 +2550,7 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A9" s="2" t="inlineStr"/>
       <c r="B9" s="2" t="inlineStr">
         <is>
           <t>111001800422</t>
@@ -2590,7 +2558,7 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO ROGELIO SALMONA (IED)</t>
+          <t>COLEGIO ROGELIO SALMONA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
@@ -2831,11 +2799,7 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A10" s="2" t="inlineStr"/>
       <c r="B10" s="2" t="inlineStr">
         <is>
           <t>111001800422</t>
@@ -2843,7 +2807,7 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO ROGELIO SALMONA (IED)</t>
+          <t>COLEGIO ROGELIO SALMONA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
@@ -3080,11 +3044,7 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A11" s="2" t="inlineStr"/>
       <c r="B11" s="2" t="inlineStr">
         <is>
           <t>111001800422</t>
@@ -3092,7 +3052,7 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO ROGELIO SALMONA (IED)</t>
+          <t>COLEGIO ROGELIO SALMONA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
@@ -3329,11 +3289,7 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A12" s="2" t="inlineStr"/>
       <c r="B12" s="2" t="inlineStr">
         <is>
           <t>111001800422</t>
@@ -3341,7 +3297,7 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO ROGELIO SALMONA (IED)</t>
+          <t>COLEGIO ROGELIO SALMONA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
@@ -3582,11 +3538,7 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A13" s="2" t="inlineStr"/>
       <c r="B13" s="2" t="inlineStr">
         <is>
           <t>111001800422</t>
@@ -3594,7 +3546,7 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO ROGELIO SALMONA (IED)</t>
+          <t>COLEGIO ROGELIO SALMONA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
@@ -3835,11 +3787,7 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A14" s="2" t="inlineStr"/>
       <c r="B14" s="2" t="inlineStr">
         <is>
           <t>111001800422</t>
@@ -3847,7 +3795,7 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO ROGELIO SALMONA (IED)</t>
+          <t>COLEGIO ROGELIO SALMONA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
@@ -4088,11 +4036,7 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A15" s="2" t="inlineStr"/>
       <c r="B15" s="2" t="inlineStr">
         <is>
           <t>111001800422</t>
@@ -4100,7 +4044,7 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO ROGELIO SALMONA (IED)</t>
+          <t>COLEGIO ROGELIO SALMONA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
@@ -4341,11 +4285,7 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A16" s="2" t="inlineStr"/>
       <c r="B16" s="2" t="inlineStr">
         <is>
           <t>111001800422</t>
@@ -4353,7 +4293,7 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO ROGELIO SALMONA (IED)</t>
+          <t>COLEGIO ROGELIO SALMONA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
@@ -4594,11 +4534,7 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A17" s="2" t="inlineStr"/>
       <c r="B17" s="2" t="inlineStr">
         <is>
           <t>111001800422</t>
@@ -4606,7 +4542,7 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO ROGELIO SALMONA (IED)</t>
+          <t>COLEGIO ROGELIO SALMONA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
@@ -4847,11 +4783,7 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A18" s="2" t="inlineStr"/>
       <c r="B18" s="2" t="inlineStr">
         <is>
           <t>111001800422</t>
@@ -4859,7 +4791,7 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO ROGELIO SALMONA (IED)</t>
+          <t>COLEGIO ROGELIO SALMONA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
@@ -5096,11 +5028,7 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A19" s="2" t="inlineStr"/>
       <c r="B19" s="2" t="inlineStr">
         <is>
           <t>111001800422</t>
@@ -5108,7 +5036,7 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO ROGELIO SALMONA (IED)</t>
+          <t>COLEGIO ROGELIO SALMONA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
@@ -5345,11 +5273,7 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A20" s="2" t="inlineStr"/>
       <c r="B20" s="2" t="inlineStr">
         <is>
           <t>111001800422</t>
@@ -5357,7 +5281,7 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO ROGELIO SALMONA (IED)</t>
+          <t>COLEGIO ROGELIO SALMONA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
@@ -5586,11 +5510,7 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A21" s="2" t="inlineStr"/>
       <c r="B21" s="2" t="inlineStr">
         <is>
           <t>111001800422</t>
@@ -5598,7 +5518,7 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO ROGELIO SALMONA (IED)</t>
+          <t>COLEGIO ROGELIO SALMONA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
@@ -5819,11 +5739,7 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A22" s="2" t="inlineStr"/>
       <c r="B22" s="2" t="inlineStr">
         <is>
           <t>111001800422</t>
@@ -5831,7 +5747,7 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO ROGELIO SALMONA (IED)</t>
+          <t>COLEGIO ROGELIO SALMONA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
@@ -6072,11 +5988,7 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A23" s="2" t="inlineStr"/>
       <c r="B23" s="2" t="inlineStr">
         <is>
           <t>111001800422</t>
@@ -6084,7 +5996,7 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO ROGELIO SALMONA (IED)</t>
+          <t>COLEGIO ROGELIO SALMONA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
@@ -6325,11 +6237,7 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A24" s="2" t="inlineStr"/>
       <c r="B24" s="2" t="inlineStr">
         <is>
           <t>111001800422</t>
@@ -6337,7 +6245,7 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO ROGELIO SALMONA (IED)</t>
+          <t>COLEGIO ROGELIO SALMONA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
@@ -6578,11 +6486,7 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A25" s="2" t="inlineStr"/>
       <c r="B25" s="2" t="inlineStr">
         <is>
           <t>111001800422</t>
@@ -6590,7 +6494,7 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO ROGELIO SALMONA (IED)</t>
+          <t>COLEGIO ROGELIO SALMONA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
@@ -6831,11 +6735,7 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A26" s="2" t="inlineStr"/>
       <c r="B26" s="2" t="inlineStr">
         <is>
           <t>111001800422</t>
@@ -6843,7 +6743,7 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO ROGELIO SALMONA (IED)</t>
+          <t>COLEGIO ROGELIO SALMONA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
@@ -7084,11 +6984,7 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A27" s="2" t="inlineStr"/>
       <c r="B27" s="2" t="inlineStr">
         <is>
           <t>111001800422</t>
@@ -7096,7 +6992,7 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO ROGELIO SALMONA (IED)</t>
+          <t>COLEGIO ROGELIO SALMONA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
@@ -7337,11 +7233,7 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A28" s="2" t="inlineStr"/>
       <c r="B28" s="2" t="inlineStr">
         <is>
           <t>111001800422</t>
@@ -7349,7 +7241,7 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO ROGELIO SALMONA (IED)</t>
+          <t>COLEGIO ROGELIO SALMONA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
@@ -7590,11 +7482,7 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A29" s="2" t="inlineStr"/>
       <c r="B29" s="2" t="inlineStr">
         <is>
           <t>111001800422</t>
@@ -7602,7 +7490,7 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO ROGELIO SALMONA (IED)</t>
+          <t>COLEGIO ROGELIO SALMONA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
@@ -7843,11 +7731,7 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A30" s="2" t="inlineStr"/>
       <c r="B30" s="2" t="inlineStr">
         <is>
           <t>111001800422</t>
@@ -7855,7 +7739,7 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO ROGELIO SALMONA (IED)</t>
+          <t>COLEGIO ROGELIO SALMONA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
@@ -8092,11 +7976,7 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A31" s="2" t="inlineStr"/>
       <c r="B31" s="2" t="inlineStr">
         <is>
           <t>111001800422</t>
@@ -8104,7 +7984,7 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO ROGELIO SALMONA (IED)</t>
+          <t>COLEGIO ROGELIO SALMONA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
@@ -8345,11 +8225,7 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A32" s="2" t="inlineStr"/>
       <c r="B32" s="2" t="inlineStr">
         <is>
           <t>111001800422</t>
@@ -8357,7 +8233,7 @@
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO ROGELIO SALMONA (IED)</t>
+          <t>COLEGIO ROGELIO SALMONA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr">
@@ -8598,11 +8474,7 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A33" s="2" t="inlineStr"/>
       <c r="B33" s="2" t="inlineStr">
         <is>
           <t>111001800422</t>
@@ -8610,7 +8482,7 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO ROGELIO SALMONA (IED)</t>
+          <t>COLEGIO ROGELIO SALMONA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
@@ -8851,11 +8723,7 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A34" s="2" t="inlineStr"/>
       <c r="B34" s="2" t="inlineStr">
         <is>
           <t>111001800422</t>
@@ -8863,7 +8731,7 @@
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO ROGELIO SALMONA (IED)</t>
+          <t>COLEGIO ROGELIO SALMONA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D34" s="2" t="inlineStr">
@@ -9104,11 +8972,7 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A35" s="2" t="inlineStr"/>
       <c r="B35" s="2" t="inlineStr">
         <is>
           <t>111001800422</t>
@@ -9116,7 +8980,7 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO ROGELIO SALMONA (IED)</t>
+          <t>COLEGIO ROGELIO SALMONA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
@@ -9357,11 +9221,7 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A36" s="2" t="inlineStr"/>
       <c r="B36" s="2" t="inlineStr">
         <is>
           <t>111001800422</t>
@@ -9369,7 +9229,7 @@
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO ROGELIO SALMONA (IED)</t>
+          <t>COLEGIO ROGELIO SALMONA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D36" s="2" t="inlineStr">
@@ -9610,11 +9470,7 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A37" s="2" t="inlineStr"/>
       <c r="B37" s="2" t="inlineStr">
         <is>
           <t>111001800422</t>
@@ -9622,7 +9478,7 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO ROGELIO SALMONA (IED)</t>
+          <t>COLEGIO ROGELIO SALMONA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
@@ -9863,11 +9719,7 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A38" s="2" t="inlineStr"/>
       <c r="B38" s="2" t="inlineStr">
         <is>
           <t>111001800422</t>
@@ -9875,7 +9727,7 @@
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO ROGELIO SALMONA (IED)</t>
+          <t>COLEGIO ROGELIO SALMONA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D38" s="2" t="inlineStr">
@@ -10116,11 +9968,7 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A39" s="2" t="inlineStr"/>
       <c r="B39" s="2" t="inlineStr">
         <is>
           <t>111001800422</t>
@@ -10128,7 +9976,7 @@
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO ROGELIO SALMONA (IED)</t>
+          <t>COLEGIO ROGELIO SALMONA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
@@ -10369,11 +10217,7 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A40" s="2" t="inlineStr"/>
       <c r="B40" s="2" t="inlineStr">
         <is>
           <t>111001800422</t>
@@ -10381,7 +10225,7 @@
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO ROGELIO SALMONA (IED)</t>
+          <t>COLEGIO ROGELIO SALMONA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D40" s="2" t="inlineStr">
@@ -10622,11 +10466,7 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A41" s="2" t="inlineStr"/>
       <c r="B41" s="2" t="inlineStr">
         <is>
           <t>111001800422</t>
@@ -10634,7 +10474,7 @@
       </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO ROGELIO SALMONA (IED)</t>
+          <t>COLEGIO ROGELIO SALMONA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D41" s="2" t="inlineStr">
@@ -10875,11 +10715,7 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A42" s="2" t="inlineStr"/>
       <c r="B42" s="2" t="inlineStr">
         <is>
           <t>111001800422</t>
@@ -10887,7 +10723,7 @@
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO ROGELIO SALMONA (IED)</t>
+          <t>COLEGIO ROGELIO SALMONA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D42" s="2" t="inlineStr">
@@ -11048,11 +10884,7 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A43" s="2" t="inlineStr"/>
       <c r="B43" s="2" t="inlineStr">
         <is>
           <t>111001800422</t>
@@ -11060,7 +10892,7 @@
       </c>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO ROGELIO SALMONA (IED)</t>
+          <t>COLEGIO ROGELIO SALMONA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D43" s="2" t="inlineStr">
@@ -11301,11 +11133,7 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A44" s="2" t="inlineStr"/>
       <c r="B44" s="2" t="inlineStr">
         <is>
           <t>111001800422</t>
@@ -11313,7 +11141,7 @@
       </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO ROGELIO SALMONA (IED)</t>
+          <t>COLEGIO ROGELIO SALMONA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D44" s="2" t="inlineStr">
@@ -11550,11 +11378,7 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A45" s="2" t="inlineStr"/>
       <c r="B45" s="2" t="inlineStr">
         <is>
           <t>111001800422</t>
@@ -11562,7 +11386,7 @@
       </c>
       <c r="C45" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO ROGELIO SALMONA (IED)</t>
+          <t>COLEGIO ROGELIO SALMONA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D45" s="2" t="inlineStr">
@@ -11803,11 +11627,7 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A46" s="2" t="inlineStr"/>
       <c r="B46" s="2" t="inlineStr">
         <is>
           <t>111001800422</t>
@@ -11815,7 +11635,7 @@
       </c>
       <c r="C46" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO ROGELIO SALMONA (IED)</t>
+          <t>COLEGIO ROGELIO SALMONA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D46" s="2" t="inlineStr">
@@ -12056,11 +11876,7 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A47" s="2" t="inlineStr"/>
       <c r="B47" s="2" t="inlineStr">
         <is>
           <t>111001800422</t>
@@ -12068,7 +11884,7 @@
       </c>
       <c r="C47" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO ROGELIO SALMONA (IED)</t>
+          <t>COLEGIO ROGELIO SALMONA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D47" s="2" t="inlineStr">
@@ -12309,11 +12125,7 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A48" s="2" t="inlineStr"/>
       <c r="B48" s="2" t="inlineStr">
         <is>
           <t>111001800422</t>
@@ -12321,7 +12133,7 @@
       </c>
       <c r="C48" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO ROGELIO SALMONA (IED)</t>
+          <t>COLEGIO ROGELIO SALMONA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D48" s="2" t="inlineStr">
@@ -12562,11 +12374,7 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A49" s="2" t="inlineStr"/>
       <c r="B49" s="2" t="inlineStr">
         <is>
           <t>111001800422</t>
@@ -12574,7 +12382,7 @@
       </c>
       <c r="C49" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO ROGELIO SALMONA (IED)</t>
+          <t>COLEGIO ROGELIO SALMONA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D49" s="2" t="inlineStr">
@@ -12815,11 +12623,7 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A50" s="2" t="inlineStr"/>
       <c r="B50" s="2" t="inlineStr">
         <is>
           <t>111001800422</t>
@@ -12827,7 +12631,7 @@
       </c>
       <c r="C50" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO ROGELIO SALMONA (IED)</t>
+          <t>COLEGIO ROGELIO SALMONA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D50" s="2" t="inlineStr">
@@ -13068,11 +12872,7 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A51" s="2" t="inlineStr"/>
       <c r="B51" s="2" t="inlineStr">
         <is>
           <t>111001800422</t>
@@ -13080,7 +12880,7 @@
       </c>
       <c r="C51" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO ROGELIO SALMONA (IED)</t>
+          <t>COLEGIO ROGELIO SALMONA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D51" s="2" t="inlineStr">
@@ -13321,11 +13121,7 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A52" s="2" t="inlineStr"/>
       <c r="B52" s="2" t="inlineStr">
         <is>
           <t>111001800422</t>
@@ -13333,7 +13129,7 @@
       </c>
       <c r="C52" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO ROGELIO SALMONA (IED)</t>
+          <t>COLEGIO ROGELIO SALMONA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D52" s="2" t="inlineStr">
@@ -13570,11 +13366,7 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A53" s="2" t="inlineStr"/>
       <c r="B53" s="2" t="inlineStr">
         <is>
           <t>111001800422</t>
@@ -13582,7 +13374,7 @@
       </c>
       <c r="C53" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO ROGELIO SALMONA (IED)</t>
+          <t>COLEGIO ROGELIO SALMONA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D53" s="2" t="inlineStr">
@@ -13823,11 +13615,7 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A54" s="2" t="inlineStr"/>
       <c r="B54" s="2" t="inlineStr">
         <is>
           <t>111001800422</t>
@@ -13835,7 +13623,7 @@
       </c>
       <c r="C54" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO ROGELIO SALMONA (IED)</t>
+          <t>COLEGIO ROGELIO SALMONA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D54" s="2" t="inlineStr">
@@ -14076,11 +13864,7 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A55" s="2" t="inlineStr"/>
       <c r="B55" s="2" t="inlineStr">
         <is>
           <t>111001800422</t>
@@ -14088,7 +13872,7 @@
       </c>
       <c r="C55" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO ROGELIO SALMONA (IED)</t>
+          <t>COLEGIO ROGELIO SALMONA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D55" s="2" t="inlineStr">
@@ -14329,11 +14113,7 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A56" s="2" t="inlineStr"/>
       <c r="B56" s="2" t="inlineStr">
         <is>
           <t>111001800422</t>
@@ -14341,7 +14121,7 @@
       </c>
       <c r="C56" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO ROGELIO SALMONA (IED)</t>
+          <t>COLEGIO ROGELIO SALMONA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D56" s="2" t="inlineStr">
@@ -14542,11 +14322,7 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A57" s="2" t="inlineStr"/>
       <c r="B57" s="2" t="inlineStr">
         <is>
           <t>111001800422</t>
@@ -14554,7 +14330,7 @@
       </c>
       <c r="C57" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO ROGELIO SALMONA (IED)</t>
+          <t>COLEGIO ROGELIO SALMONA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D57" s="2" t="inlineStr">
@@ -14795,11 +14571,7 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A58" s="2" t="inlineStr"/>
       <c r="B58" s="2" t="inlineStr">
         <is>
           <t>111001800422</t>
@@ -14807,7 +14579,7 @@
       </c>
       <c r="C58" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO ROGELIO SALMONA (IED)</t>
+          <t>COLEGIO ROGELIO SALMONA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D58" s="2" t="inlineStr">
@@ -15048,11 +14820,7 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A59" s="2" t="inlineStr"/>
       <c r="B59" s="2" t="inlineStr">
         <is>
           <t>111001800422</t>
@@ -15060,7 +14828,7 @@
       </c>
       <c r="C59" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO ROGELIO SALMONA (IED)</t>
+          <t>COLEGIO ROGELIO SALMONA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D59" s="2" t="inlineStr">
@@ -15301,11 +15069,7 @@
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A60" s="2" t="inlineStr"/>
       <c r="B60" s="2" t="inlineStr">
         <is>
           <t>111001800422</t>
@@ -15313,7 +15077,7 @@
       </c>
       <c r="C60" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO ROGELIO SALMONA (IED)</t>
+          <t>COLEGIO ROGELIO SALMONA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D60" s="2" t="inlineStr">
@@ -15554,11 +15318,7 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A61" s="2" t="inlineStr"/>
       <c r="B61" s="2" t="inlineStr">
         <is>
           <t>111001800422</t>
@@ -15566,7 +15326,7 @@
       </c>
       <c r="C61" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO ROGELIO SALMONA (IED)</t>
+          <t>COLEGIO ROGELIO SALMONA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D61" s="2" t="inlineStr">
@@ -15807,11 +15567,7 @@
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A62" s="2" t="inlineStr"/>
       <c r="B62" s="2" t="inlineStr">
         <is>
           <t>111001800422</t>
@@ -15819,7 +15575,7 @@
       </c>
       <c r="C62" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO ROGELIO SALMONA (IED)</t>
+          <t>COLEGIO ROGELIO SALMONA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D62" s="2" t="inlineStr">
@@ -16060,11 +15816,7 @@
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A63" s="2" t="inlineStr"/>
       <c r="B63" s="2" t="inlineStr">
         <is>
           <t>111001800422</t>
@@ -16072,7 +15824,7 @@
       </c>
       <c r="C63" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO ROGELIO SALMONA (IED)</t>
+          <t>COLEGIO ROGELIO SALMONA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D63" s="2" t="inlineStr">
@@ -16313,11 +16065,7 @@
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A64" s="2" t="inlineStr"/>
       <c r="B64" s="2" t="inlineStr">
         <is>
           <t>111001800422</t>
@@ -16325,7 +16073,7 @@
       </c>
       <c r="C64" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO ROGELIO SALMONA (IED)</t>
+          <t>COLEGIO ROGELIO SALMONA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D64" s="2" t="inlineStr">
@@ -16566,11 +16314,7 @@
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A65" s="2" t="inlineStr"/>
       <c r="B65" s="2" t="inlineStr">
         <is>
           <t>111001800422</t>
@@ -16578,7 +16322,7 @@
       </c>
       <c r="C65" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO ROGELIO SALMONA (IED)</t>
+          <t>COLEGIO ROGELIO SALMONA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D65" s="2" t="inlineStr">
@@ -16819,11 +16563,7 @@
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A66" s="2" t="inlineStr"/>
       <c r="B66" s="2" t="inlineStr">
         <is>
           <t>111001800422</t>
@@ -16831,7 +16571,7 @@
       </c>
       <c r="C66" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO ROGELIO SALMONA (IED)</t>
+          <t>COLEGIO ROGELIO SALMONA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D66" s="2" t="inlineStr">
@@ -17072,11 +16812,7 @@
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A67" s="2" t="inlineStr"/>
       <c r="B67" s="2" t="inlineStr">
         <is>
           <t>111001800422</t>
@@ -17084,7 +16820,7 @@
       </c>
       <c r="C67" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO ROGELIO SALMONA (IED)</t>
+          <t>COLEGIO ROGELIO SALMONA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D67" s="2" t="inlineStr">
@@ -17325,11 +17061,7 @@
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A68" s="2" t="inlineStr"/>
       <c r="B68" s="2" t="inlineStr">
         <is>
           <t>111001800422</t>
@@ -17337,7 +17069,7 @@
       </c>
       <c r="C68" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO ROGELIO SALMONA (IED)</t>
+          <t>COLEGIO ROGELIO SALMONA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D68" s="2" t="inlineStr">
@@ -17578,11 +17310,7 @@
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A69" s="2" t="inlineStr"/>
       <c r="B69" s="2" t="inlineStr">
         <is>
           <t>111001800422</t>
@@ -17590,7 +17318,7 @@
       </c>
       <c r="C69" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO ROGELIO SALMONA (IED)</t>
+          <t>COLEGIO ROGELIO SALMONA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D69" s="2" t="inlineStr">
@@ -17831,11 +17559,7 @@
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A70" s="2" t="inlineStr"/>
       <c r="B70" s="2" t="inlineStr">
         <is>
           <t>111001800422</t>
@@ -17843,7 +17567,7 @@
       </c>
       <c r="C70" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO ROGELIO SALMONA (IED)</t>
+          <t>COLEGIO ROGELIO SALMONA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D70" s="2" t="inlineStr">
@@ -18084,11 +17808,7 @@
       </c>
     </row>
     <row r="71">
-      <c r="A71" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A71" s="2" t="inlineStr"/>
       <c r="B71" s="2" t="inlineStr">
         <is>
           <t>111001800422</t>
@@ -18096,7 +17816,7 @@
       </c>
       <c r="C71" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO ROGELIO SALMONA (IED)</t>
+          <t>COLEGIO ROGELIO SALMONA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D71" s="2" t="inlineStr">
@@ -18333,11 +18053,7 @@
       </c>
     </row>
     <row r="72">
-      <c r="A72" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A72" s="2" t="inlineStr"/>
       <c r="B72" s="2" t="inlineStr">
         <is>
           <t>111001800422</t>
@@ -18345,7 +18061,7 @@
       </c>
       <c r="C72" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO ROGELIO SALMONA (IED)</t>
+          <t>COLEGIO ROGELIO SALMONA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D72" s="2" t="inlineStr">
@@ -18586,11 +18302,7 @@
       </c>
     </row>
     <row r="73">
-      <c r="A73" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A73" s="2" t="inlineStr"/>
       <c r="B73" s="2" t="inlineStr">
         <is>
           <t>111001800422</t>
@@ -18598,7 +18310,7 @@
       </c>
       <c r="C73" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO ROGELIO SALMONA (IED)</t>
+          <t>COLEGIO ROGELIO SALMONA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D73" s="2" t="inlineStr">
@@ -18839,11 +18551,7 @@
       </c>
     </row>
     <row r="74">
-      <c r="A74" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A74" s="2" t="inlineStr"/>
       <c r="B74" s="2" t="inlineStr">
         <is>
           <t>111001800422</t>
@@ -18851,7 +18559,7 @@
       </c>
       <c r="C74" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO ROGELIO SALMONA (IED)</t>
+          <t>COLEGIO ROGELIO SALMONA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D74" s="2" t="inlineStr">
@@ -19088,11 +18796,7 @@
       </c>
     </row>
     <row r="75">
-      <c r="A75" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A75" s="2" t="inlineStr"/>
       <c r="B75" s="2" t="inlineStr">
         <is>
           <t>111001800422</t>
@@ -19100,7 +18804,7 @@
       </c>
       <c r="C75" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO ROGELIO SALMONA (IED)</t>
+          <t>COLEGIO ROGELIO SALMONA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D75" s="2" t="inlineStr">
@@ -19341,11 +19045,7 @@
       </c>
     </row>
     <row r="76">
-      <c r="A76" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A76" s="2" t="inlineStr"/>
       <c r="B76" s="2" t="inlineStr">
         <is>
           <t>111001800422</t>
@@ -19353,7 +19053,7 @@
       </c>
       <c r="C76" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO ROGELIO SALMONA (IED)</t>
+          <t>COLEGIO ROGELIO SALMONA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D76" s="2" t="inlineStr">
@@ -19594,11 +19294,7 @@
       </c>
     </row>
     <row r="77">
-      <c r="A77" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A77" s="2" t="inlineStr"/>
       <c r="B77" s="2" t="inlineStr">
         <is>
           <t>111001800422</t>
@@ -19606,7 +19302,7 @@
       </c>
       <c r="C77" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO ROGELIO SALMONA (IED)</t>
+          <t>COLEGIO ROGELIO SALMONA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D77" s="2" t="inlineStr">
@@ -19847,11 +19543,7 @@
       </c>
     </row>
     <row r="78">
-      <c r="A78" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A78" s="2" t="inlineStr"/>
       <c r="B78" s="2" t="inlineStr">
         <is>
           <t>111001800422</t>
@@ -19859,7 +19551,7 @@
       </c>
       <c r="C78" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO ROGELIO SALMONA (IED)</t>
+          <t>COLEGIO ROGELIO SALMONA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D78" s="2" t="inlineStr">
@@ -20100,11 +19792,7 @@
       </c>
     </row>
     <row r="79">
-      <c r="A79" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A79" s="2" t="inlineStr"/>
       <c r="B79" s="2" t="inlineStr">
         <is>
           <t>111001800422</t>
@@ -20112,7 +19800,7 @@
       </c>
       <c r="C79" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO ROGELIO SALMONA (IED)</t>
+          <t>COLEGIO ROGELIO SALMONA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D79" s="2" t="inlineStr">
@@ -20353,11 +20041,7 @@
       </c>
     </row>
     <row r="80">
-      <c r="A80" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A80" s="2" t="inlineStr"/>
       <c r="B80" s="2" t="inlineStr">
         <is>
           <t>111001800422</t>
@@ -20365,7 +20049,7 @@
       </c>
       <c r="C80" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO ROGELIO SALMONA (IED)</t>
+          <t>COLEGIO ROGELIO SALMONA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D80" s="2" t="inlineStr">
@@ -20602,11 +20286,7 @@
       </c>
     </row>
     <row r="81">
-      <c r="A81" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A81" s="2" t="inlineStr"/>
       <c r="B81" s="2" t="inlineStr">
         <is>
           <t>111001800422</t>
@@ -20614,7 +20294,7 @@
       </c>
       <c r="C81" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO ROGELIO SALMONA (IED)</t>
+          <t>COLEGIO ROGELIO SALMONA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D81" s="2" t="inlineStr">
@@ -20855,11 +20535,7 @@
       </c>
     </row>
     <row r="82">
-      <c r="A82" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A82" s="2" t="inlineStr"/>
       <c r="B82" s="2" t="inlineStr">
         <is>
           <t>111001800422</t>
@@ -20867,7 +20543,7 @@
       </c>
       <c r="C82" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO ROGELIO SALMONA (IED)</t>
+          <t>COLEGIO ROGELIO SALMONA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D82" s="2" t="inlineStr">
@@ -21108,11 +20784,7 @@
       </c>
     </row>
     <row r="83">
-      <c r="A83" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A83" s="2" t="inlineStr"/>
       <c r="B83" s="2" t="inlineStr">
         <is>
           <t>111001800422</t>
@@ -21120,7 +20792,7 @@
       </c>
       <c r="C83" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO ROGELIO SALMONA (IED)</t>
+          <t>COLEGIO ROGELIO SALMONA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D83" s="2" t="inlineStr">
@@ -21361,11 +21033,7 @@
       </c>
     </row>
     <row r="84">
-      <c r="A84" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A84" s="2" t="inlineStr"/>
       <c r="B84" s="2" t="inlineStr">
         <is>
           <t>111001800422</t>
@@ -21373,7 +21041,7 @@
       </c>
       <c r="C84" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO ROGELIO SALMONA (IED)</t>
+          <t>COLEGIO ROGELIO SALMONA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D84" s="2" t="inlineStr">
@@ -21614,11 +21282,7 @@
       </c>
     </row>
     <row r="85">
-      <c r="A85" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A85" s="2" t="inlineStr"/>
       <c r="B85" s="2" t="inlineStr">
         <is>
           <t>111001800422</t>
@@ -21626,7 +21290,7 @@
       </c>
       <c r="C85" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO ROGELIO SALMONA (IED)</t>
+          <t>COLEGIO ROGELIO SALMONA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D85" s="2" t="inlineStr">
@@ -21867,11 +21531,7 @@
       </c>
     </row>
     <row r="86">
-      <c r="A86" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A86" s="2" t="inlineStr"/>
       <c r="B86" s="2" t="inlineStr">
         <is>
           <t>111001800422</t>
@@ -21879,7 +21539,7 @@
       </c>
       <c r="C86" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO ROGELIO SALMONA (IED)</t>
+          <t>COLEGIO ROGELIO SALMONA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D86" s="2" t="inlineStr">
@@ -22120,11 +21780,7 @@
       </c>
     </row>
     <row r="87">
-      <c r="A87" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A87" s="2" t="inlineStr"/>
       <c r="B87" s="2" t="inlineStr">
         <is>
           <t>111001800422</t>
@@ -22132,7 +21788,7 @@
       </c>
       <c r="C87" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO ROGELIO SALMONA (IED)</t>
+          <t>COLEGIO ROGELIO SALMONA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D87" s="2" t="inlineStr">
@@ -22373,11 +22029,7 @@
       </c>
     </row>
     <row r="88">
-      <c r="A88" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A88" s="2" t="inlineStr"/>
       <c r="B88" s="2" t="inlineStr">
         <is>
           <t>111001800422</t>
@@ -22385,7 +22037,7 @@
       </c>
       <c r="C88" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO ROGELIO SALMONA (IED)</t>
+          <t>COLEGIO ROGELIO SALMONA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D88" s="2" t="inlineStr">
@@ -22626,11 +22278,7 @@
       </c>
     </row>
     <row r="89">
-      <c r="A89" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A89" s="2" t="inlineStr"/>
       <c r="B89" s="2" t="inlineStr">
         <is>
           <t>111001800422</t>
@@ -22638,7 +22286,7 @@
       </c>
       <c r="C89" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO ROGELIO SALMONA (IED)</t>
+          <t>COLEGIO ROGELIO SALMONA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D89" s="2" t="inlineStr">
